--- a/output/full_scan/batch_seq7_2026-06-23.xlsx
+++ b/output/full_scan/batch_seq7_2026-06-23.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O125"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1004,21 +1004,21 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6672</v>
+        <v>6488</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>745.9842022153899</v>
+        <v>758.4472610922257</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>249</v>
+        <v>1010</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>64.34555762527276</v>
+        <v>59.88687687807897</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>27.94501313611524</v>
+        <v>26.5512002287283</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.7606957010625602</v>
+        <v>0.2764517199938228</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>2.178326974950941</v>
+        <v>14.52778076733773</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6670</v>
+        <v>6672</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>745.3230598214747</v>
+        <v>745.9842022153899</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>287</v>
+        <v>249</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>57.9653889177712</v>
+        <v>64.34555762527276</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>35.83362242210934</v>
+        <v>27.94501313611524</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.309667537161938</v>
+        <v>0.7606957010625602</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.8378336682158505</v>
+        <v>2.178326974950941</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6494</v>
+        <v>6670</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>744.6851987432946</v>
+        <v>745.3230598214747</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>68.59999999999999</v>
+        <v>287</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>69.06858904406742</v>
+        <v>57.9653889177712</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>35.23098961696752</v>
+        <v>35.83362242210934</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.660741464025618</v>
+        <v>1.309667537161938</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.330148250403519</v>
+        <v>0.8378336682158505</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6684</v>
+        <v>6494</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>744</v>
+        <v>744.6851987432946</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>60.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>77.07172588567119</v>
+        <v>69.06858904406742</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>27.34946364294231</v>
+        <v>35.23098961696752</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>7.483262742611619</v>
+        <v>1.660741464025618</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.137417465899127</v>
+        <v>1.330148250403519</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6651</v>
+        <v>6684</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>733.5616031514292</v>
+        <v>744</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>153</v>
+        <v>60.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>60.67685728863818</v>
+        <v>77.07172588567119</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>33.4680585062754</v>
+        <v>27.34946364294231</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.62474517156701</v>
+        <v>7.483262742611619</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.141626941960441</v>
+        <v>1.137417465899127</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6691</v>
+        <v>6651</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>717.8046255537058</v>
+        <v>733.5616031514292</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>712</v>
+        <v>153</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>59.11802505193823</v>
+        <v>60.67685728863818</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>22.66930639192958</v>
+        <v>33.4680585062754</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.6013520724784082</v>
+        <v>1.62474517156701</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>7.35415851876726</v>
+        <v>1.141626941960441</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6531</v>
+        <v>6613</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>715.4517162106847</v>
+        <v>727.692041394052</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1050</v>
+        <v>368</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>55.67992775901922</v>
+        <v>72.48246244237239</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>24.87496367247221</v>
+        <v>38.45209767700332</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.224921351874534</v>
+        <v>0.6320499076763932</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.3529804727709624</v>
+        <v>10.51156353699102</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6666</v>
+        <v>6691</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>711.7905566952834</v>
+        <v>717.8046255537058</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>43.3</v>
+        <v>712</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>61.65962013401766</v>
+        <v>59.11802505193823</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>33.07690452469802</v>
+        <v>22.66930639192958</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.6355856091313873</v>
+        <v>0.6013520724784082</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.2011002420763113</v>
+        <v>7.35415851876726</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6541</v>
+        <v>6531</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>711.7741526840653</v>
+        <v>715.4517162106847</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>43.85</v>
+        <v>1050</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>66.43455756149368</v>
+        <v>55.67992775901922</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>17.77060341440592</v>
+        <v>24.87496367247221</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.910457279244103</v>
+        <v>1.224921351874534</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.3319139755418454</v>
+        <v>0.3529804727709624</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6693</v>
+        <v>6666</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>694.6696822196949</v>
+        <v>711.7905566952834</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>236.5</v>
+        <v>43.3</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>78.12142297162598</v>
+        <v>61.65962013401766</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>48.09075960453509</v>
+        <v>33.07690452469802</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.264160077402434</v>
+        <v>0.6355856091313873</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>7.723427867133619</v>
+        <v>0.2011002420763113</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6668</v>
+        <v>6541</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>691.5151308976123</v>
+        <v>711.7741526840653</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>42.5</v>
+        <v>43.85</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>55.87511383066318</v>
+        <v>66.43455756149368</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>33.41819083562388</v>
+        <v>17.77060341440592</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.7515130897612236</v>
+        <v>1.910457279244103</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.5448258467333318</v>
+        <v>0.3319139755418454</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6592</v>
+        <v>6693</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>683.3569892285843</v>
+        <v>694.6696822196949</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>65.5</v>
+        <v>236.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>59.93693976851706</v>
+        <v>78.12142297162598</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>31.14735022676492</v>
+        <v>48.09075960453509</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5642188214891901</v>
+        <v>2.264160077402434</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.0599883939274629</v>
+        <v>7.723427867133619</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6679</v>
+        <v>6668</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>662.7914357554713</v>
+        <v>691.5151308976123</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>284.5</v>
+        <v>42.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,49 +1665,49 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>48.30904233470418</v>
+        <v>55.87511383066318</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>21.72309286467342</v>
+        <v>33.41819083562388</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5366013492426395</v>
+        <v>0.7515130897612236</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.239399549755527</v>
+        <v>0.5448258467333318</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, invest_trust_buy_2d</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6573</v>
+        <v>6592</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>654.3507696875976</v>
+        <v>683.3569892285843</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>19.55</v>
+        <v>65.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>72.90128223175799</v>
+        <v>59.93693976851706</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>15.27053514641286</v>
+        <v>31.14735022676492</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>4.035076968759761</v>
+        <v>0.5642188214891901</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.2628670222212067</v>
+        <v>0.0599883939274629</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6642</v>
+        <v>6679</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>643.876266043383</v>
+        <v>662.7914357554713</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>87.59999999999999</v>
+        <v>284.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>57.72780663354173</v>
+        <v>48.30904233470418</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>48.62108378651433</v>
+        <v>21.72309286467342</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5472873004431631</v>
+        <v>0.5366013492426395</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.3804096658901814</v>
+        <v>0.239399549755527</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6667</v>
+        <v>6573</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>643.5725235161181</v>
+        <v>654.3507696875976</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>276</v>
+        <v>19.55</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>52.98499188437544</v>
+        <v>72.90128223175799</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>13.00257696690473</v>
+        <v>15.27053514641286</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.017583160482985</v>
+        <v>4.035076968759761</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.9738167491018496</v>
+        <v>0.2628670222212067</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6556</v>
+        <v>6642</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>642.3039302909681</v>
+        <v>643.876266043383</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>50.27271528346191</v>
+        <v>57.72780663354173</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>44.29963857213989</v>
+        <v>48.62108378651433</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.7734876764823726</v>
+        <v>0.5472873004431631</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.0829972073408852</v>
+        <v>-0.3804096658901814</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6491</v>
+        <v>6667</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>634.4660872816825</v>
+        <v>643.5725235161181</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>325.5</v>
+        <v>276</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>60.22818987228764</v>
+        <v>52.98499188437544</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>26.35484726865024</v>
+        <v>13.00257696690473</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4222625004479433</v>
+        <v>1.017583160482985</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.9027164251189888</v>
+        <v>0.9738167491018496</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6625</v>
+        <v>6556</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>634.1944862921613</v>
+        <v>642.3039302909681</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>78.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>62.74671785060368</v>
+        <v>50.27271528346191</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>30.66244656305265</v>
+        <v>44.29963857213989</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.053803576033235</v>
+        <v>0.7734876764823726</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.4762098832604232</v>
+        <v>-0.0829972073408852</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6821</v>
+        <v>6491</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>633.7862736453555</v>
+        <v>634.4660872816825</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>64.90000000000001</v>
+        <v>325.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>51.79966700234866</v>
+        <v>60.22818987228764</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>23.79300658656773</v>
+        <v>26.35484726865024</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.051845918548445</v>
+        <v>0.4222625004479433</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.5784855380221816</v>
+        <v>-0.9027164251189888</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6834</v>
+        <v>6625</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>630.3454751665065</v>
+        <v>634.1944862921613</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>111.5</v>
+        <v>78.2</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>75.41572087394786</v>
+        <v>62.74671785060368</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>47.45722367259146</v>
+        <v>30.66244656305265</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.586355912490983</v>
+        <v>1.053803576033235</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>2.746019444297936</v>
+        <v>0.4762098832604232</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6585</v>
+        <v>6821</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>628.7908260473968</v>
+        <v>633.7862736453555</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>144.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>76.73848442586159</v>
+        <v>51.79966700234866</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>64.36286601009307</v>
+        <v>23.79300658656773</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.041189019401762</v>
+        <v>1.051845918548445</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>2.411137830246341</v>
+        <v>-0.5784855380221816</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6517</v>
+        <v>6834</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>624.1917798665326</v>
+        <v>630.3454751665065</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>111.5</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>62.91214291347147</v>
+        <v>75.41572087394786</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>37.33516027418696</v>
+        <v>47.45722367259146</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.195402285746904</v>
+        <v>2.586355912490983</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>1.127270317336178</v>
+        <v>2.746019444297936</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6742</v>
+        <v>6585</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>616.1551453857752</v>
+        <v>628.7908260473968</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>144.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>69.15650606489811</v>
+        <v>76.73848442586159</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>34.90063496297026</v>
+        <v>64.36286601009307</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.411195402825913</v>
+        <v>1.041189019401762</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.8105385192478436</v>
+        <v>2.411137830246341</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6579</v>
+        <v>6517</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>609.2522633745973</v>
+        <v>624.1917798665326</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>158.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>50.04183336405578</v>
+        <v>62.91214291347147</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>32.2339416017245</v>
+        <v>37.33516027418696</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.6992483839545097</v>
+        <v>1.195402285746904</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-1.562218971425207</v>
+        <v>1.127270317336178</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6658</v>
+        <v>6742</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>605.5457366494919</v>
+        <v>616.1551453857752</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>187.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>52.5289170234182</v>
+        <v>69.15650606489811</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>29.260299229351</v>
+        <v>34.90063496297026</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.6501770600095974</v>
+        <v>1.411195402825913</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-3.193021628692182</v>
+        <v>0.8105385192478436</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6725</v>
+        <v>6579</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>604.8361244831361</v>
+        <v>609.2522633745973</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>341</v>
+        <v>158.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>57.06848266934171</v>
+        <v>50.04183336405578</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>21.26246558925832</v>
+        <v>32.2339416017245</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.815430742555716</v>
+        <v>0.6992483839545097</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>6.381254281005605</v>
+        <v>-1.562218971425207</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6654</v>
+        <v>6658</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>600.4074208135687</v>
+        <v>605.5457366494919</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>199</v>
+        <v>187.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>68.01691937117587</v>
+        <v>52.5289170234182</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>50.92508090467949</v>
+        <v>29.260299229351</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.1771007216224</v>
+        <v>0.6501770600095974</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>2.124973384846214</v>
+        <v>-3.193021628692182</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6756</v>
+        <v>6725</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>593.7553420021111</v>
+        <v>604.8361244831361</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>105</v>
+        <v>341</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>58.25438355540535</v>
+        <v>57.06848266934171</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>27.86330909733942</v>
+        <v>21.26246558925832</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.183191827115572</v>
+        <v>0.815430742555716</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.5776198978069895</v>
+        <v>6.381254281005605</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6698</v>
+        <v>6654</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>583.8408909407277</v>
+        <v>600.4074208135687</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>44.1</v>
+        <v>199</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>65.6775178275779</v>
+        <v>68.01691937117587</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>33.78348836645819</v>
+        <v>50.92508090467949</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.6769785143771869</v>
+        <v>1.1771007216224</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.1387865941379884</v>
+        <v>2.124973384846214</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6719</v>
+        <v>6756</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>579.5321721964067</v>
+        <v>593.7553420021111</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>277.5</v>
+        <v>105</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>67.27299779714681</v>
+        <v>58.25438355540535</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>42.10564059614153</v>
+        <v>27.86330909733942</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.680924979238654</v>
+        <v>1.183191827115572</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>3.574014485894081</v>
+        <v>0.5776198978069895</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6716</v>
+        <v>6698</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>579.3701600037708</v>
+        <v>583.8408909407277</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>101.5</v>
+        <v>44.1</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>55.4152093710048</v>
+        <v>65.6775178275779</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>30.517925978632</v>
+        <v>33.78348836645819</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.645106243703491</v>
+        <v>0.6769785143771869</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.1301874647917549</v>
+        <v>0.1387865941379884</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6560</v>
+        <v>6719</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>576.1836478335406</v>
+        <v>579.5321721964067</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>39.4</v>
+        <v>277.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>57.1666773675488</v>
+        <v>67.27299779714681</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>16.60528586385063</v>
+        <v>42.10564059614153</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.53148379608351</v>
+        <v>2.680924979238654</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0861768384805142</v>
+        <v>3.574014485894081</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6790</v>
+        <v>6716</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>571.142565530557</v>
+        <v>579.3701600037708</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>40.2</v>
+        <v>101.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>59.88878985672546</v>
+        <v>55.4152093710048</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>18.00321076005402</v>
+        <v>30.517925978632</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.048669634508616</v>
+        <v>0.645106243703491</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.07740803828901389</v>
+        <v>0.1301874647917549</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6683</v>
+        <v>6560</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>556.0830680652075</v>
+        <v>576.1836478335406</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1765</v>
+        <v>39.4</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,49 +2831,49 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>54.20433933151472</v>
+        <v>57.1666773675488</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>15.04461327259236</v>
+        <v>16.60528586385063</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.894860299546424</v>
+        <v>1.53148379608351</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>24.13896668637481</v>
+        <v>0.0861768384805142</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6526</v>
+        <v>6790</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>551.9973076529033</v>
+        <v>571.142565530557</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>697</v>
+        <v>40.2</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>56.88915556701539</v>
+        <v>59.88878985672546</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>16.37347354516513</v>
+        <v>18.00321076005402</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.922089992417558</v>
+        <v>1.048669634508616</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>2.137855023648997</v>
+        <v>0.07740803828901389</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6789</v>
+        <v>6683</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>549.8697855879263</v>
+        <v>556.0830680652075</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>552</v>
+        <v>1765</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,49 +2937,49 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>58.54217400041171</v>
+        <v>54.20433933151472</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>18.45383459328753</v>
+        <v>15.04461327259236</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.346800906590445</v>
+        <v>1.894860299546424</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>5.324064677162529</v>
+        <v>24.13896668637481</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6695</v>
+        <v>6526</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>534.3531504726326</v>
+        <v>551.9973076529033</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>62.7</v>
+        <v>697</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>62.94264900834557</v>
+        <v>56.88915556701539</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>26.96397984444638</v>
+        <v>16.37347354516513</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.544020292853898</v>
+        <v>0.922089992417558</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.7647128750958876</v>
+        <v>2.137855023648997</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6498</v>
+        <v>6789</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>533.9156511265999</v>
+        <v>549.8697855879263</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>101.5</v>
+        <v>552</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>49.34003112765319</v>
+        <v>58.54217400041171</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>30.83749289894177</v>
+        <v>18.45383459328753</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.823247056972381</v>
+        <v>1.346800906590445</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,48 +3061,48 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.0202285085577402</v>
+        <v>5.324064677162529</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6806</v>
+        <v>6695</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>533.7768356926886</v>
+        <v>534.3531504726326</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>3.51</v>
+        <v>62.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G50" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>31.69502801993506</v>
+        <v>62.94264900834557</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>32.59319589058759</v>
+        <v>26.96397984444638</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>2.544020292853898</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.4112821522523093</v>
+        <v>0.7647128750958876</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6512</v>
+        <v>6498</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>513.9074035212645</v>
+        <v>533.9156511265999</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>19.9</v>
+        <v>101.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>52.27566011458969</v>
+        <v>49.34003112765319</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>8.542249744725112</v>
+        <v>30.83749289894177</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.7279950644402411</v>
+        <v>0.823247056972381</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,48 +3167,48 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.09639995782188961</v>
+        <v>-0.0202285085577402</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6690</v>
+        <v>6806</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>512.3325735756915</v>
+        <v>533.7768356926886</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>176</v>
+        <v>3.51</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G52" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>50.92302580008206</v>
+        <v>31.69502801993506</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>19.50358614018689</v>
+        <v>32.59319589058759</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7335379913296751</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.306206631356015</v>
+        <v>0.4112821522523093</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6645</v>
+        <v>6512</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>511.7688228309563</v>
+        <v>513.9074035212645</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>16.15</v>
+        <v>19.9</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>67.99008766345497</v>
+        <v>52.27566011458969</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>44.36173380717288</v>
+        <v>8.542249744725112</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.002459256436583</v>
+        <v>0.7279950644402411</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.3936273441466802</v>
+        <v>0.09639995782188961</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6515</v>
+        <v>6690</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>489.3169471659968</v>
+        <v>512.3325735756915</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>9450</v>
+        <v>176</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>53.27305543711826</v>
+        <v>50.92302580008206</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>19.219487316882</v>
+        <v>19.50358614018689</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7195926461025355</v>
+        <v>0.7335379913296751</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>100.8375386824715</v>
+        <v>-0.306206631356015</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6788</v>
+        <v>6645</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>486.160235949428</v>
+        <v>511.7688228309563</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>429</v>
+        <v>16.15</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>50.07775390477629</v>
+        <v>67.99008766345497</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>8.605030981592115</v>
+        <v>44.36173380717288</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.7219672441801553</v>
+        <v>1.002459256436583</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.8301672382013354</v>
+        <v>0.3936273441466802</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6811</v>
+        <v>6515</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>481.7654457124116</v>
+        <v>489.3169471659968</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>226.5</v>
+        <v>9450</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>52.65433822063392</v>
+        <v>53.27305543711826</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>23.20142146404818</v>
+        <v>19.219487316882</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.6980257596181096</v>
+        <v>0.7195926461025355</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-1.561365105299895</v>
+        <v>100.8375386824715</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6589</v>
+        <v>6788</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>480.0267141209765</v>
+        <v>486.160235949428</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>46.55</v>
+        <v>429</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>57.66377946151344</v>
+        <v>50.07775390477629</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>16.71289527409576</v>
+        <v>8.605030981592115</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.8238017555131252</v>
+        <v>0.7219672441801553</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.4527816990265662</v>
+        <v>0.8301672382013354</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6799</v>
+        <v>6811</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>475.187181907466</v>
+        <v>481.7654457124116</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>105</v>
+        <v>226.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>60.24402904935134</v>
+        <v>52.65433822063392</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>28.29930597748505</v>
+        <v>23.20142146404818</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.213343872558099</v>
+        <v>0.6980257596181096</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.9649656175929648</v>
+        <v>-1.561365105299895</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6761</v>
+        <v>6589</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>469.1218764804453</v>
+        <v>480.0267141209765</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>208</v>
+        <v>46.55</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.08284420269613</v>
+        <v>57.66377946151344</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>20.36204161327329</v>
+        <v>16.71289527409576</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.9620087197275879</v>
+        <v>0.8238017555131252</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.1506211859079349</v>
+        <v>0.4527816990265662</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6584</v>
+        <v>6799</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>467.6954132241716</v>
+        <v>475.187181907466</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>649</v>
+        <v>105</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>50.696732281589</v>
+        <v>60.24402904935134</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>11.5539485622003</v>
+        <v>28.29930597748505</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.8128651732118849</v>
+        <v>1.213343872558099</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1.26055438362922</v>
+        <v>0.9649656175929648</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6570</v>
+        <v>6761</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>453.3647618544869</v>
+        <v>469.1218764804453</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>52.8</v>
+        <v>208</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>47.34911446207632</v>
+        <v>52.08284420269613</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>23.01454747744091</v>
+        <v>20.36204161327329</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.3571376021517717</v>
+        <v>0.9620087197275879</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-1.128041155484758</v>
+        <v>-0.1506211859079349</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6582</v>
+        <v>6584</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>448.6236662758997</v>
+        <v>467.6954132241716</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>32.2</v>
+        <v>649</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>61.97429973503314</v>
+        <v>50.696732281589</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>24.44735790242196</v>
+        <v>11.5539485622003</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.40262155747115</v>
+        <v>0.8128651732118849</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0837460241728718</v>
+        <v>1.26055438362922</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6754</v>
+        <v>6570</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>448.549726880167</v>
+        <v>453.3647618544869</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>45.5</v>
+        <v>52.8</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>54.14743575246718</v>
+        <v>47.34911446207632</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>22.78925612931175</v>
+        <v>23.01454747744091</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3542125361842818</v>
+        <v>0.3571376021517717</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.07088204448075321</v>
+        <v>-1.128041155484758</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6792</v>
+        <v>6582</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>448.3306649058077</v>
+        <v>448.6236662758997</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>32.2</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>51.04780940948508</v>
+        <v>61.97429973503314</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>33.5071617046022</v>
+        <v>24.44735790242196</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5509547201611411</v>
+        <v>1.40262155747115</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.484675660075913</v>
+        <v>0.0837460241728718</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6781</v>
+        <v>6754</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>430.1887927761334</v>
+        <v>448.549726880167</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>1170</v>
+        <v>45.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>51.08048007738114</v>
+        <v>54.14743575246718</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>13.29284389000629</v>
+        <v>22.78925612931175</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.7446386615450644</v>
+        <v>0.3542125361842818</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>3.217338773582202</v>
+        <v>0.07088204448075321</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6505</v>
+        <v>6792</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>425.9955998124266</v>
+        <v>448.3306649058077</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>52.1</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>47.12607159298363</v>
+        <v>51.04780940948508</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>12.257417395138</v>
+        <v>33.5071617046022</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.7301750051190599</v>
+        <v>0.5509547201611411</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0249693546686322</v>
+        <v>-0.484675660075913</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6532</v>
+        <v>6781</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>414.1896786838012</v>
+        <v>430.1887927761334</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>90.5</v>
+        <v>1170</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45.23898353251515</v>
+        <v>51.08048007738114</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>21.11869486785161</v>
+        <v>13.29284389000629</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.479705745896903</v>
+        <v>0.7446386615450644</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.4581960048353808</v>
+        <v>3.217338773582202</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6735</v>
+        <v>6505</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>409.7927878329567</v>
+        <v>425.9955998124266</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>96.3</v>
+        <v>52.1</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>46.22414017748545</v>
+        <v>47.12607159298363</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.53233351870306</v>
+        <v>12.257417395138</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.739658773428812</v>
+        <v>0.7301750051190599</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.3182787385004317</v>
+        <v>0.0249693546686322</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6782</v>
+        <v>6532</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>409.1934737701745</v>
+        <v>414.1896786838012</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>194</v>
+        <v>90.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>47.47805830553362</v>
+        <v>45.23898353251515</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>9.000659979126738</v>
+        <v>21.11869486785161</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.5066555757747726</v>
+        <v>0.479705745896903</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.4798963422853783</v>
+        <v>-0.4581960048353808</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6743</v>
+        <v>6735</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>408.2923284645571</v>
+        <v>409.7927878329567</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>29.8</v>
+        <v>96.3</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>57.82062146009446</v>
+        <v>46.22414017748545</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>18.04320367993164</v>
+        <v>15.53233351870306</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.161423604992423</v>
+        <v>1.739658773428812</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.1312623414088591</v>
+        <v>-0.3182787385004317</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6605</v>
+        <v>6782</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>381.5622750314933</v>
+        <v>409.1934737701745</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>137.5</v>
+        <v>194</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>46.89431997801759</v>
+        <v>47.47805830553362</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>19.11747341544075</v>
+        <v>9.000659979126738</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.7132894935891873</v>
+        <v>0.5066555757747726</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.9322214891618814</v>
+        <v>0.4798963422853783</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6674</v>
+        <v>6743</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>372.057025558802</v>
+        <v>408.2923284645571</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>17.65</v>
+        <v>29.8</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>48.77842181803477</v>
+        <v>57.82062146009446</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16.2651076688339</v>
+        <v>18.04320367993164</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5255652938808986</v>
+        <v>1.161423604992423</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0088032950571196</v>
+        <v>-0.1312623414088591</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6720</v>
+        <v>6605</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>367.4210052918501</v>
+        <v>381.5622750314933</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>140.5</v>
+        <v>137.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>29.39739551781012</v>
+        <v>46.89431997801759</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>31.33580214817543</v>
+        <v>19.11747341544075</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.450303342079935</v>
+        <v>0.7132894935891873</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.4727358499463463</v>
+        <v>-0.9322214891618814</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6597</v>
+        <v>6674</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>360.814712239343</v>
+        <v>372.057025558802</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>68.5</v>
+        <v>17.65</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>48.32964858066115</v>
+        <v>48.77842181803477</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>10.42347609098247</v>
+        <v>16.2651076688339</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.3939088207467544</v>
+        <v>0.5255652938808986</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.5832922002949049</v>
+        <v>0.0088032950571196</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6692</v>
+        <v>6720</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>360.7071153476509</v>
+        <v>367.4210052918501</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>26.05</v>
+        <v>140.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>41.7623731986854</v>
+        <v>29.39739551781012</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>20.52385038379314</v>
+        <v>31.33580214817543</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.2544101285892097</v>
+        <v>0.450303342079935</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.2635562087937022</v>
+        <v>-0.4727358499463463</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6643</v>
+        <v>6597</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>358.2912153620135</v>
+        <v>360.814712239343</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>490.5</v>
+        <v>68.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>40.46496816432481</v>
+        <v>48.32964858066115</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>24.51971017979652</v>
+        <v>10.42347609098247</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6185567010309279</v>
+        <v>0.3939088207467544</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-2.142068282766999</v>
+        <v>-0.5832922002949049</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6840</v>
+        <v>6692</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>355.048826618995</v>
+        <v>360.7071153476509</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>65.3</v>
+        <v>26.05</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>47.5634470519303</v>
+        <v>41.7623731986854</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>18.39760304189986</v>
+        <v>20.52385038379314</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6025354886735733</v>
+        <v>0.2544101285892097</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.1162131780805</v>
+        <v>0.2635562087937022</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6763</v>
+        <v>6643</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>352.5534054969777</v>
+        <v>358.2912153620135</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>46.25</v>
+        <v>490.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>46.2509761111889</v>
+        <v>40.46496816432481</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>21.29150836714168</v>
+        <v>24.51971017979652</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.448466481173205</v>
+        <v>0.6185567010309279</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.0164592438719788</v>
+        <v>-2.142068282766999</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6588</v>
+        <v>6840</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>342.3827781314351</v>
+        <v>355.048826618995</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>101.5</v>
+        <v>65.3</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>37.65698334336755</v>
+        <v>47.5634470519303</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>15.04918030851508</v>
+        <v>18.39760304189986</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.4822172387091584</v>
+        <v>0.6025354886735733</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.4279082224165274</v>
+        <v>-0.1162131780805</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6727</v>
+        <v>6763</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>340.3024185380683</v>
+        <v>352.5534054969777</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>450</v>
+        <v>46.25</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>47.7625540037006</v>
+        <v>46.2509761111889</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19.47046816771583</v>
+        <v>21.29150836714168</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.928160083335957</v>
+        <v>0.448466481173205</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-4.211387344948005</v>
+        <v>-0.0164592438719788</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6624</v>
+        <v>6588</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>335.632663035696</v>
+        <v>342.3827781314351</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>40.5</v>
+        <v>101.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>49.99980586007958</v>
+        <v>37.65698334336755</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>11.58394237143308</v>
+        <v>15.04918030851508</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.2552830348807604</v>
+        <v>0.4822172387091584</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.192357986611444</v>
+        <v>0.4279082224165274</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6581</v>
+        <v>6727</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>335.0902751235434</v>
+        <v>340.3024185380683</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>108.5</v>
+        <v>450</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>49.76498655155802</v>
+        <v>47.7625540037006</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>11.65165309919253</v>
+        <v>19.47046816771583</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.4690529937648545</v>
+        <v>0.928160083335957</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0618705440371158</v>
+        <v>-4.211387344948005</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6829</v>
+        <v>6624</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>332.459324900383</v>
+        <v>335.632663035696</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>206</v>
+        <v>40.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>49.81814827472579</v>
+        <v>49.99980586007958</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>13.4815597635871</v>
+        <v>11.58394237143308</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.7605121262959292</v>
+        <v>0.2552830348807604</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.3423092771450544</v>
+        <v>0.192357986611444</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6664</v>
+        <v>6581</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>331.7614307070332</v>
+        <v>335.0902751235434</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>376.5</v>
+        <v>108.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>41.55123328855312</v>
+        <v>49.76498655155802</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>24.29323914853275</v>
+        <v>11.65165309919253</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.5927642468895933</v>
+        <v>0.4690529937648545</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-1.288412153536496</v>
+        <v>-0.0618705440371158</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6558</v>
+        <v>6829</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>326.4483545249472</v>
+        <v>332.459324900383</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>30.65</v>
+        <v>206</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>46.10348809036936</v>
+        <v>49.81814827472579</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>22.20720727947837</v>
+        <v>13.4815597635871</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4222916212073135</v>
+        <v>0.7605121262959292</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.2426863402408002</v>
+        <v>-0.3423092771450544</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6706</v>
+        <v>6664</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>323.3875416923727</v>
+        <v>331.7614307070332</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>163.5</v>
+        <v>376.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>44.27153274820331</v>
+        <v>41.55123328855312</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16.52511165813995</v>
+        <v>24.29323914853275</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3659011444030279</v>
+        <v>0.5927642468895933</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-3.179363203922929</v>
+        <v>-1.288412153536496</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6598</v>
+        <v>6558</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>319.8774431787958</v>
+        <v>326.4483545249472</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>23.45</v>
+        <v>30.65</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>39.7301773951702</v>
+        <v>46.10348809036936</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>22.07372473801992</v>
+        <v>22.20720727947837</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.6512940626343851</v>
+        <v>0.4222916212073135</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.1767369246799114</v>
+        <v>-0.2426863402408002</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6655</v>
+        <v>6706</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>310.4495637720889</v>
+        <v>323.3875416923727</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>124.5</v>
+        <v>163.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>51.28340313794268</v>
+        <v>44.27153274820331</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>15.8100478795475</v>
+        <v>16.52511165813995</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5657729939448729</v>
+        <v>0.3659011444030279</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-4.324122121057869</v>
+        <v>-3.179363203922929</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, williams_r_recovery</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6568</v>
+        <v>6598</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>307.6277603591737</v>
+        <v>319.8774431787958</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>178</v>
+        <v>23.45</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>38.03020977373409</v>
+        <v>39.7301773951702</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>27.09176983268223</v>
+        <v>22.07372473801992</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6525787453707013</v>
+        <v>0.6512940626343851</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.9250499367523854</v>
+        <v>-0.1767369246799114</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6606</v>
+        <v>6655</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>306.224528019532</v>
+        <v>310.4495637720889</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>24.8</v>
+        <v>124.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>38.19134245070239</v>
+        <v>51.28340313794268</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>19.50630581715591</v>
+        <v>15.8100478795475</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4425016761876231</v>
+        <v>0.5657729939448729</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.2178847040855474</v>
+        <v>-4.324122121057869</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6753</v>
+        <v>6568</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>305.2350979087792</v>
+        <v>307.6277603591737</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>51.72140633487151</v>
+        <v>38.03020977373409</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>15.95176594522166</v>
+        <v>27.09176983268223</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.9360228261633722</v>
+        <v>0.6525787453707013</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.8762239699251571</v>
+        <v>-0.9250499367523854</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6552</v>
+        <v>6606</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>299.4535255095825</v>
+        <v>306.224528019532</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>31.7</v>
+        <v>24.8</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>51.81650009738009</v>
+        <v>38.19134245070239</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>16.55366371462567</v>
+        <v>19.50630581715591</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7883069892377202</v>
+        <v>0.4425016761876231</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0529936100079789</v>
+        <v>-0.2178847040855474</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6669</v>
+        <v>6753</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>298.5491962113559</v>
+        <v>305.2350979087792</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>4675</v>
+        <v>126</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>40.56850987954667</v>
+        <v>51.72140633487151</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>17.62238578115655</v>
+        <v>15.95176594522166</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.9946453965494952</v>
+        <v>0.9360228261633722</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-81.53031674036296</v>
+        <v>0.8762239699251571</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6640</v>
+        <v>6552</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>295.4182381974705</v>
+        <v>299.4535255095825</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>1050</v>
+        <v>31.7</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>35.27265091107098</v>
+        <v>51.81650009738009</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>25.54312221998825</v>
+        <v>16.55366371462567</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6021964978312506</v>
+        <v>0.7883069892377202</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-2.835834509976096</v>
+        <v>-0.0529936100079789</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6550</v>
+        <v>6669</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>295.3611755891507</v>
+        <v>298.5491962113559</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>13.1</v>
+        <v>4675</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>34.36120641467426</v>
+        <v>40.56850987954667</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>33.24673676720325</v>
+        <v>17.62238578115655</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4189732423422942</v>
+        <v>0.9946453965494952</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.17968733937248</v>
+        <v>-81.53031674036296</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6796</v>
+        <v>6640</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>290.8477767696615</v>
+        <v>295.4182381974705</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>59.2</v>
+        <v>1050</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>40.64838192202874</v>
+        <v>35.27265091107098</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>30.24179225089697</v>
+        <v>25.54312221998825</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6540320107004037</v>
+        <v>0.6021964978312506</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.2795270578133353</v>
+        <v>-2.835834509976096</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6776</v>
+        <v>6550</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>288.6877651489952</v>
+        <v>295.3611755891507</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>58.3</v>
+        <v>13.1</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>44.37358154208055</v>
+        <v>34.36120641467426</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>8.468328757073724</v>
+        <v>33.24673676720325</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.9155324334769604</v>
+        <v>0.4189732423422942</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.2032686917470088</v>
+        <v>0.17968733937248</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6530</v>
+        <v>6796</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>286.0355848384412</v>
+        <v>290.8477767696615</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>59.2</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>40.69352523048472</v>
+        <v>40.64838192202874</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>15.51612751417769</v>
+        <v>30.24179225089697</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.5871011708623718</v>
+        <v>0.6540320107004037</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.8545339806301433</v>
+        <v>0.2795270578133353</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6739</v>
+        <v>6776</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>272.8551368156045</v>
+        <v>288.6877651489952</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>1120</v>
+        <v>58.3</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>41.71665527321606</v>
+        <v>44.37358154208055</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>11.78801913958071</v>
+        <v>8.468328757073724</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.9310115195692188</v>
+        <v>0.9155324334769604</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-1.89875788314724</v>
+        <v>-0.2032686917470088</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6680</v>
+        <v>6530</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>251.256199657423</v>
+        <v>286.0355848384412</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>51</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>50.76408916857723</v>
+        <v>40.69352523048472</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>6.258219803601015</v>
+        <v>15.51612751417769</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6778188557583713</v>
+        <v>0.5871011708623718</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>1.068765052664456</v>
+        <v>-0.8545339806301433</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6805</v>
+        <v>6739</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>247.7405124707403</v>
+        <v>272.8551368156045</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>1765</v>
+        <v>1120</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45.5739261953299</v>
+        <v>41.71665527321606</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>13.42924343661604</v>
+        <v>11.78801913958071</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.3389280181466114</v>
+        <v>0.9310115195692188</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-12.76011275476864</v>
+        <v>-1.89875788314724</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6533</v>
+        <v>6680</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>247.7311794030228</v>
+        <v>251.256199657423</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>206.5</v>
+        <v>51</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>44.95832667700358</v>
+        <v>50.76408916857723</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>15.21843485088124</v>
+        <v>6.258219803601015</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6918204381998573</v>
+        <v>0.6778188557583713</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.6648548470416893</v>
+        <v>1.068765052664456</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6546</v>
+        <v>6805</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>244.4288855237263</v>
+        <v>247.7405124707403</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>73</v>
+        <v>1765</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>46.15108576132614</v>
+        <v>45.5739261953299</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.0357064548007</v>
+        <v>13.42924343661604</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5332985941999882</v>
+        <v>0.3389280181466114</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.6569805428944389</v>
+        <v>-12.76011275476864</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6708</v>
+        <v>6533</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>239.6786264150476</v>
+        <v>247.7311794030228</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>40.35</v>
+        <v>206.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>51.44937836598459</v>
+        <v>44.95832667700358</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>15.59695582624029</v>
+        <v>15.21843485088124</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.163242318265779</v>
+        <v>0.6918204381998573</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.08707867019558491</v>
+        <v>-0.6648548470416893</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6614</v>
+        <v>6546</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>237.7454071646601</v>
+        <v>244.4288855237263</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>39.95</v>
+        <v>73</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>47.43953314908718</v>
+        <v>46.15108576132614</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>16.71944754232941</v>
+        <v>18.0357064548007</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.6453052123214023</v>
+        <v>0.5332985941999882</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0939069080632929</v>
+        <v>-0.6569805428944389</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6657</v>
+        <v>6708</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>228.4625727547838</v>
+        <v>239.6786264150476</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>35.25</v>
+        <v>40.35</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>38.86790105467234</v>
+        <v>51.44937836598459</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>21.34565955607683</v>
+        <v>15.59695582624029</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.3815174826411991</v>
+        <v>1.163242318265779</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.07092685591483371</v>
+        <v>0.08707867019558491</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6803</v>
+        <v>6614</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>224.8035636387671</v>
+        <v>237.7454071646601</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>286.5</v>
+        <v>39.95</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>46.54342861910424</v>
+        <v>47.43953314908718</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>27.63790733276278</v>
+        <v>16.71944754232941</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.051533422168872</v>
+        <v>0.6453052123214023</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0469837309550351</v>
+        <v>0.0939069080632929</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6741</v>
+        <v>6657</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>223.8055452800678</v>
+        <v>228.4625727547838</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>62.5</v>
+        <v>35.25</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>49.0633642395345</v>
+        <v>38.86790105467234</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.11721444622808</v>
+        <v>21.34565955607683</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.6104778678352338</v>
+        <v>0.3815174826411991</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.0465543546934178</v>
+        <v>0.07092685591483371</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6641</v>
+        <v>6803</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>223.3265757096869</v>
+        <v>224.8035636387671</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>18.25</v>
+        <v>286.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>46.35633347477594</v>
+        <v>46.54342861910424</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>17.37576406130656</v>
+        <v>27.63790733276278</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.9310558360686974</v>
+        <v>1.051533422168872</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.006079677579913</v>
+        <v>0.0469837309550351</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6823</v>
+        <v>6741</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>214.1760586199795</v>
+        <v>223.8055452800678</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>71.5</v>
+        <v>62.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>47.58390493363315</v>
+        <v>49.0633642395345</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>21.79493928925094</v>
+        <v>12.11721444622808</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5863697636597439</v>
+        <v>0.6104778678352338</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.624788182133956</v>
+        <v>0.0465543546934178</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6771</v>
+        <v>6641</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>204.5248245609901</v>
+        <v>223.3265757096869</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>42.05</v>
+        <v>18.25</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>47.05841450139026</v>
+        <v>46.35633347477594</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>12.19585494341458</v>
+        <v>17.37576406130656</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6559394536649055</v>
+        <v>0.9310558360686974</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.099775135630706</v>
+        <v>0.006079677579913</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6504</v>
+        <v>6823</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>201.7457995332745</v>
+        <v>214.1760586199795</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>36.2</v>
+        <v>71.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>38.80479957600008</v>
+        <v>47.58390493363315</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>18.92288383452225</v>
+        <v>21.79493928925094</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.7010994702210522</v>
+        <v>0.5863697636597439</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.1286387203422696</v>
+        <v>0.624788182133956</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6722</v>
+        <v>6771</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>194.8857323438012</v>
+        <v>204.5248245609901</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>36</v>
+        <v>42.05</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>33.62272439275695</v>
+        <v>47.05841450139026</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>16.84062838096528</v>
+        <v>12.19585494341458</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.512206191188626</v>
+        <v>0.6559394536649055</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.2397840275484658</v>
+        <v>0.099775135630706</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6794</v>
+        <v>6504</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>189.5582387948581</v>
+        <v>201.7457995332745</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>79.2</v>
+        <v>36.2</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.96876276109524</v>
+        <v>38.80479957600008</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>13.23992394205302</v>
+        <v>18.92288383452225</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.268353231650395</v>
+        <v>0.7010994702210522</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.2144435726704208</v>
+        <v>0.1286387203422696</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6534</v>
+        <v>6722</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>186.1979338988448</v>
+        <v>194.8857323438012</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>92.2</v>
+        <v>36</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>48.90916668350344</v>
+        <v>33.62272439275695</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>15.89544218934994</v>
+        <v>16.84062838096528</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.4433180027969358</v>
+        <v>1.512206191188626</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.282999906328732</v>
+        <v>-0.2397840275484658</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6577</v>
+        <v>6794</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>180.2945941642988</v>
+        <v>189.5582387948581</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>74.8</v>
+        <v>79.2</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>29.57112131601578</v>
+        <v>42.96876276109524</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>16.80555868334465</v>
+        <v>13.23992394205302</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.9294594164298764</v>
+        <v>1.268353231650395</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.700192098007404</v>
+        <v>-0.2144435726704208</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6838</v>
+        <v>6534</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>175.2813044570072</v>
+        <v>186.1979338988448</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>23.75</v>
+        <v>92.2</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>28.47352919858575</v>
+        <v>48.90916668350344</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>11.01343544080896</v>
+        <v>15.89544218934994</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.747602752352001</v>
+        <v>0.4433180027969358</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0298126092195873</v>
+        <v>0.282999906328732</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6486</v>
+        <v>6577</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>169.1664284062964</v>
+        <v>180.2945941642988</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>42.0054914125061</v>
+        <v>29.57112131601578</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>15.35074106926763</v>
+        <v>16.80555868334465</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.7947920518028754</v>
+        <v>0.9294594164298764</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0620930755422808</v>
+        <v>-0.700192098007404</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6768</v>
+        <v>6838</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>168.4603074468059</v>
+        <v>175.2813044570072</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>87.2</v>
+        <v>23.75</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>46.65168478995075</v>
+        <v>28.47352919858575</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>18.4269063054417</v>
+        <v>11.01343544080896</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.4655437619765462</v>
+        <v>1.747602752352001</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.8861943485530324</v>
+        <v>-0.0298126092195873</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6671</v>
+        <v>6486</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>167.6248414597485</v>
+        <v>169.1664284062964</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>24.85</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>25.44708533211588</v>
+        <v>42.0054914125061</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>19.91169667088106</v>
+        <v>15.35074106926763</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.7896870420858106</v>
+        <v>0.7947920518028754</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.0237872695438063</v>
+        <v>0.0620930755422808</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6591</v>
+        <v>6768</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>167.3813122301616</v>
+        <v>168.4603074468059</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>54.2</v>
+        <v>87.2</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>43.00389946894926</v>
+        <v>46.65168478995075</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>20.72894852329999</v>
+        <v>18.4269063054417</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.4964231679690581</v>
+        <v>0.4655437619765462</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.1563051597171664</v>
+        <v>-0.8861943485530324</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6807</v>
+        <v>6671</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>150.0736901402674</v>
+        <v>167.6248414597485</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>33.2</v>
+        <v>24.85</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>39.84228752635093</v>
+        <v>25.44708533211588</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>24.68835062449214</v>
+        <v>19.91169667088106</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.1644047315681745</v>
+        <v>0.7896870420858106</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.1522677305394516</v>
+        <v>-0.0237872695438063</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6835</v>
+        <v>6591</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>140.1618274291722</v>
+        <v>167.3813122301616</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>36.5</v>
+        <v>54.2</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>42.64131149441899</v>
+        <v>43.00389946894926</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>13.41184102672874</v>
+        <v>20.72894852329999</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.1531000932575735</v>
+        <v>0.4964231679690581</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.0714516080399875</v>
+        <v>-0.1563051597171664</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6689</v>
+        <v>6807</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>112.3398099931427</v>
+        <v>150.0736901402674</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>66.40000000000001</v>
+        <v>33.2</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>42.1373318087399</v>
+        <v>39.84228752635093</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>12.22420598322783</v>
+        <v>24.68835062449214</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.4625238471459079</v>
+        <v>0.1644047315681745</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,62 +7036,168 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.3121926587585154</v>
+        <v>0.1522677305394516</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
+        <v>6835</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>圓裕</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>140.1618274291722</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>42.64131149441899</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>13.41184102672874</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.1531000932575735</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>-0.0714516080399875</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>6689</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>伊雲谷</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>112.3398099931427</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>42.1373318087399</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>12.22420598322783</v>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.4625238471459079</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
+        <v>-0.3121926587585154</v>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
         <v>6561</v>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>是方</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D125" s="2" t="n">
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
         <v>70.3438905375957</v>
       </c>
-      <c r="E125" s="2" t="n">
+      <c r="E127" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H125" s="2" t="n">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
         <v>42.36525558406976</v>
       </c>
-      <c r="I125" s="2" t="n">
+      <c r="I127" s="2" t="n">
         <v>15.1961737300739</v>
       </c>
-      <c r="J125" s="2" t="n">
+      <c r="J127" s="2" t="n">
         <v>0.6244748519708987</v>
       </c>
-      <c r="K125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N125" s="2" t="n">
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
         <v>-1.664401330034454</v>
       </c>
-      <c r="O125" s="2" t="inlineStr">
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq7_2026-06-23.xlsx
+++ b/output/full_scan/batch_seq7_2026-06-23.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6538</v>
+        <v>6831</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>997.7430722833916</v>
+        <v>1208.581226615291</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>138</v>
+        <v>830</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,29 +552,29 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>67.78581145595476</v>
+        <v>64.59871566004767</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>31.88993500303632</v>
+        <v>26.02465658217042</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3.294801635371101</v>
+        <v>1.121620093882147</v>
       </c>
       <c r="K2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.6923243514742072</v>
+        <v>0.2523674851793842</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>853.9004410142272</v>
+        <v>1203.900441014227</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>569</v>
@@ -605,49 +605,49 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>69.04876350236154</v>
+        <v>69.04876350971247</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>24.48862916171099</v>
+        <v>24.48862915802341</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>3.367408761542052</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>13.17435499786252</v>
+        <v>13.17435499745045</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6548</v>
+        <v>6538</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>828.4434411421377</v>
+        <v>1197.743072283392</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>92.7</v>
+        <v>138</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>64.98966509895502</v>
+        <v>67.78581147123816</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46.17063292431217</v>
+        <v>31.8899350147984</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.529847933981047</v>
+        <v>3.294801635371101</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>2</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.0615589551102004</v>
+        <v>0.6923243512887609</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6757</v>
+        <v>6531</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>815.3777606083994</v>
+        <v>1035.451716210685</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>61.3</v>
+        <v>1050</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>65.6389732115545</v>
+        <v>55.67992777177835</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>29.51015394037839</v>
+        <v>24.8749637358147</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.13777606083994</v>
+        <v>1.224921351874534</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4792510760348571</v>
+        <v>0.3529804713284861</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6525</v>
+        <v>6757</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>810.4090789923948</v>
+        <v>1005.377760608399</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>170.5</v>
+        <v>61.3</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>81.14526106579439</v>
+        <v>65.63897336299242</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>32.69208184604781</v>
+        <v>29.51015392040703</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>3.140907899239486</v>
+        <v>1.13777606083994</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>3.831625279387438</v>
+        <v>0.4792510757875892</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6831</v>
+        <v>6525</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>803.5812266152909</v>
+        <v>985.4090789923948</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>830</v>
+        <v>170.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>64.59871565628028</v>
+        <v>81.1452610791177</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>26.02465660902054</v>
+        <v>32.69208182185655</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.121620093882147</v>
+        <v>3.140907899239486</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,11 +835,11 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.2523674852618001</v>
+        <v>3.831625279222589</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>797.4975926816069</v>
+        <v>972.5543987536456</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>78.59999999999999</v>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>57.91623479265043</v>
+        <v>57.91623479817997</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>24.29798052770055</v>
+        <v>24.29798053581723</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.879144264066489</v>
+        <v>1.887492848830068</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.0510053034744406</v>
+        <v>0.0510053034229214</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6732</v>
+        <v>6684</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>768.3216067711254</v>
+        <v>944</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>169.5</v>
+        <v>60.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>56.26980406482338</v>
+        <v>77.07172597253911</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>21.53610373356929</v>
+        <v>27.34946370326981</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.625683564530402</v>
+        <v>7.483262742611619</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.4063929366032954</v>
+        <v>1.137417465610647</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6510</v>
+        <v>6672</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>764.2326417661282</v>
+        <v>920.98420221539</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3665</v>
+        <v>249</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>54.94801520074286</v>
+        <v>64.34555764345518</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>16.14830712874098</v>
+        <v>27.94501326165119</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.500933502920775</v>
+        <v>0.7606957010625602</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>36.34772507685867</v>
+        <v>2.17832697470368</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6488</v>
+        <v>6732</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>758.4472610922257</v>
+        <v>908.3216067711254</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1010</v>
+        <v>169.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>59.88687687807897</v>
+        <v>56.26980413585635</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>26.5512002287283</v>
+        <v>21.53610371998784</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.2764517199938228</v>
+        <v>1.625683564530402</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>14.52778076733773</v>
+        <v>0.4063929357790661</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6672</v>
+        <v>6651</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>745.9842022153899</v>
+        <v>903.5616031514292</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>249</v>
+        <v>153</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>64.34555762527276</v>
+        <v>60.67685732106712</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>27.94501313611524</v>
+        <v>33.46805851244793</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.7606957010625602</v>
+        <v>1.62474517156701</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>2.178326974950941</v>
+        <v>1.141626941651374</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6670</v>
+        <v>6719</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>745.3230598214747</v>
+        <v>889.5321721964067</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>287</v>
+        <v>277.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>57.9653889177712</v>
+        <v>67.27299779535147</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>35.83362242210934</v>
+        <v>42.10564059695531</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.309667537161938</v>
+        <v>2.680924979238654</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,11 +1153,11 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.8378336682158505</v>
+        <v>3.574014485997091</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>744.6851987432946</v>
+        <v>884.6851987432946</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>68.59999999999999</v>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>69.06858904406742</v>
+        <v>69.06858908421354</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>35.23098961696752</v>
+        <v>35.23098968931575</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1.660741464025618</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.330148250403519</v>
+        <v>1.330148250228375</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6684</v>
+        <v>6573</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>744</v>
+        <v>864.3507696875976</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>60.5</v>
+        <v>19.55</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>77.07172588567119</v>
+        <v>72.90128225270824</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>27.34946364294231</v>
+        <v>15.27053505276005</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7.483262742611619</v>
+        <v>4.035076968759761</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.137417465899127</v>
+        <v>0.2628670222006015</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6651</v>
+        <v>6541</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>733.5616031514292</v>
+        <v>861.7741526840654</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>153</v>
+        <v>43.85</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>60.67685728863818</v>
+        <v>66.43455763285306</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>33.4680585062754</v>
+        <v>17.7706034294587</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.62474517156701</v>
+        <v>1.910457279244103</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1.141626941960441</v>
+        <v>0.3319139752739695</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6613</v>
+        <v>6526</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>727.692041394052</v>
+        <v>856.9973076529033</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>368</v>
+        <v>697</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>72.48246244237239</v>
+        <v>56.88915562523369</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>38.45209767700332</v>
+        <v>16.37347355437953</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.6320499076763932</v>
+        <v>0.922089992417558</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>10.51156353699102</v>
+        <v>2.137855020970205</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6691</v>
+        <v>6695</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>717.8046255537058</v>
+        <v>854.3531504726326</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>712</v>
+        <v>62.7</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>59.11802505193823</v>
+        <v>62.94264904956778</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>22.66930639192958</v>
+        <v>26.96397982648975</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.6013520724784082</v>
+        <v>2.544020292853898</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>7.35415851876726</v>
+        <v>0.7647128749310375</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6531</v>
+        <v>6742</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>715.4517162106847</v>
+        <v>846.1551453857753</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1050</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>55.67992775901922</v>
+        <v>69.15650610846744</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>24.87496367247221</v>
+        <v>34.90063494907124</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.224921351874534</v>
+        <v>1.411195402825913</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.3529804727709624</v>
+        <v>0.8105385191036003</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6666</v>
+        <v>6548</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>711.7905566952834</v>
+        <v>828.4434411421377</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>43.3</v>
+        <v>92.7</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>61.65962013401766</v>
+        <v>64.98966509071835</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>33.07690452469802</v>
+        <v>46.1706329753256</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.6355856091313873</v>
+        <v>2.529847933981047</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.2011002420763113</v>
+        <v>-0.061558955192611</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6541</v>
+        <v>6670</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>711.7741526840653</v>
+        <v>820.3230598214743</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>43.85</v>
+        <v>287</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>66.43455756149368</v>
+        <v>57.96538872320297</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>17.77060341440592</v>
+        <v>35.83362261068547</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.910457279244103</v>
+        <v>1.309667537161938</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.3319139755418454</v>
+        <v>0.8378336700703368</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6693</v>
+        <v>6698</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>694.6696822196949</v>
+        <v>813.8408909407277</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>236.5</v>
+        <v>44.1</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>78.12142297162598</v>
+        <v>65.67751786334783</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>48.09075960453509</v>
+        <v>33.78348838346363</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.264160077402434</v>
+        <v>0.6769785143771869</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>7.723427867133619</v>
+        <v>0.1387865940349599</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6668</v>
+        <v>6834</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>691.5151308976123</v>
+        <v>800.3454751665065</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>42.5</v>
+        <v>111.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>55.87511383066318</v>
+        <v>75.41572085168698</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>33.41819083562388</v>
+        <v>47.45722361813352</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.7515130897612236</v>
+        <v>2.586355912490983</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.5448258467333318</v>
+        <v>2.746019444442187</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6592</v>
+        <v>6668</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>683.3569892285843</v>
+        <v>781.5151308976123</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>65.5</v>
+        <v>42.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>59.93693976851706</v>
+        <v>55.87511393295527</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>31.14735022676492</v>
+        <v>33.41819091437416</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.5642188214891901</v>
+        <v>0.7515130897612236</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0599883939274629</v>
+        <v>0.544825846424239</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6679</v>
+        <v>6756</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>662.7914357554713</v>
+        <v>778.7553420021111</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>284.5</v>
+        <v>105</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>48.30904233470418</v>
+        <v>58.25438361300462</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>21.72309286467342</v>
+        <v>27.86330910312834</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5366013492426395</v>
+        <v>1.183191827115572</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.239399549755527</v>
+        <v>0.577619897374257</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, invest_trust_buy_2d</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6573</v>
+        <v>6691</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>654.3507696875976</v>
+        <v>777.8046255537057</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>19.55</v>
+        <v>712</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>72.90128223175799</v>
+        <v>59.11802507593831</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>15.27053514641286</v>
+        <v>22.66930633027978</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>4.035076968759761</v>
+        <v>0.6013520724784082</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.2628670222212067</v>
+        <v>7.354158518561157</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6642</v>
+        <v>6679</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>643.876266043383</v>
+        <v>777.7914357554713</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>87.59999999999999</v>
+        <v>284.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>57.72780663354173</v>
+        <v>48.3090423983074</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>48.62108378651433</v>
+        <v>21.72309290931361</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5472873004431631</v>
+        <v>0.5366013492426395</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.3804096658901814</v>
+        <v>0.2393995488282669</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6667</v>
+        <v>6725</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>643.5725235161181</v>
+        <v>774.8361244831361</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>276</v>
+        <v>341</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>52.98499188437544</v>
+        <v>57.06848267898443</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>13.00257696690473</v>
+        <v>21.26246558255429</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.017583160482985</v>
+        <v>0.815430742555716</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.9738167491018496</v>
+        <v>6.38125428038742</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6556</v>
+        <v>6510</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>642.3039302909681</v>
+        <v>764.2326417661283</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>3665</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>50.27271528346191</v>
+        <v>54.94801522480219</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>44.29963857213989</v>
+        <v>16.14830722395183</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7734876764823726</v>
+        <v>1.500933502920775</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.0829972073408852</v>
+        <v>36.34772507232529</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6491</v>
+        <v>6517</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>634.4660872816825</v>
+        <v>764.1917798665319</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>325.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>60.22818987228764</v>
+        <v>62.91214301978769</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>26.35484726865024</v>
+        <v>37.33516039501789</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4222625004479433</v>
+        <v>1.195402285746904</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.9027164251189888</v>
+        <v>1.127270316718012</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6625</v>
+        <v>6488</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>634.1944862921613</v>
+        <v>758.4472610922257</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>78.2</v>
+        <v>1010</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>62.74671785060368</v>
+        <v>59.88687687807897</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>30.66244656305265</v>
+        <v>26.5512002287283</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.053803576033235</v>
+        <v>0.2764517199938228</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.4762098832604232</v>
+        <v>14.52778076733773</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6821</v>
+        <v>6585</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>633.7862736453555</v>
+        <v>728.7908260473968</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>64.90000000000001</v>
+        <v>144.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>51.79966700234866</v>
+        <v>76.73848449300064</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>23.79300658656773</v>
+        <v>64.36286601009307</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.051845918548445</v>
+        <v>1.041189019401762</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.5784855380221816</v>
+        <v>2.411137829731198</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6834</v>
+        <v>6613</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>630.3454751665065</v>
+        <v>727.692041394052</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>111.5</v>
+        <v>368</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>75.41572087394786</v>
+        <v>72.48246244237239</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>47.45722367259146</v>
+        <v>38.45209767700332</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2.586355912490983</v>
+        <v>0.6320499076763932</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>2.746019444297936</v>
+        <v>10.51156353699102</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6585</v>
+        <v>6683</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>628.7908260473968</v>
+        <v>726.0830680652076</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>144.5</v>
+        <v>1765</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,49 +2248,49 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>76.73848442586159</v>
+        <v>54.20433934195466</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>64.36286601009307</v>
+        <v>15.04461337517652</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.041189019401762</v>
+        <v>1.894860299546424</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>2.411137830246341</v>
+        <v>24.1389666847264</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6517</v>
+        <v>6491</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>624.1917798665326</v>
+        <v>719.4660872816825</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>325.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>62.91214291347147</v>
+        <v>60.22818982431029</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>37.33516027418696</v>
+        <v>26.35484729533659</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.195402285746904</v>
+        <v>0.4222625004479433</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>1.127270317336178</v>
+        <v>-0.9027164241917092</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6742</v>
+        <v>6716</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>616.1551453857752</v>
+        <v>719.3701600037708</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>101.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>69.15650606489811</v>
+        <v>55.41520938887629</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>34.90063496297026</v>
+        <v>30.51792596151255</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.411195402825913</v>
+        <v>0.645106243703491</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.8105385192478436</v>
+        <v>0.1301874648535701</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6579</v>
+        <v>6654</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>609.2522633745973</v>
+        <v>715.4074208135687</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>158.5</v>
+        <v>199</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>50.04183336405578</v>
+        <v>68.0169193617895</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>32.2339416017245</v>
+        <v>50.92508090721701</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6992483839545097</v>
+        <v>1.1771007216224</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-1.562218971425207</v>
+        <v>2.124973384846214</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6658</v>
+        <v>6693</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>605.5457366494919</v>
+        <v>694.6696822196949</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>187.5</v>
+        <v>236.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,49 +2460,49 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>52.5289170234182</v>
+        <v>78.12142297162598</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>29.260299229351</v>
+        <v>48.09075960453509</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6501770600095974</v>
+        <v>2.264160077402434</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-3.193021628692182</v>
+        <v>7.723427867133619</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6725</v>
+        <v>6560</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>604.8361244831361</v>
+        <v>691.1836478335408</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>341</v>
+        <v>39.4</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>57.06848266934171</v>
+        <v>57.16667766565203</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>21.26246558925832</v>
+        <v>16.60528591136843</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.815430742555716</v>
+        <v>1.53148379608351</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>6.381254281005605</v>
+        <v>0.0861768380890013</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6654</v>
+        <v>6592</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>600.4074208135687</v>
+        <v>683.3569892285843</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>199</v>
+        <v>65.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,49 +2566,49 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>68.01691937117587</v>
+        <v>59.93693993513067</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>50.92508090467949</v>
+        <v>31.14735023443707</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.1771007216224</v>
+        <v>0.5642188214891901</v>
       </c>
       <c r="K40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>2.124973384846214</v>
+        <v>0.0599883938244372</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6756</v>
+        <v>6789</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>593.7553420021111</v>
+        <v>679.8697855879263</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>105</v>
+        <v>552</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>58.25438355540535</v>
+        <v>58.54217402737093</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>27.86330909733942</v>
+        <v>18.4538345841062</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.183191827115572</v>
+        <v>1.346800906590445</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.5776198978069895</v>
+        <v>5.324064676441286</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6698</v>
+        <v>6799</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>583.8408909407277</v>
+        <v>675.187181907466</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>44.1</v>
+        <v>105</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>65.6775178275779</v>
+        <v>60.24402924177125</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>33.78348836645819</v>
+        <v>28.29930602518927</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6769785143771869</v>
+        <v>1.213343872558099</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.1387865941379884</v>
+        <v>0.9649656156354222</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6719</v>
+        <v>6666</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>579.5321721964067</v>
+        <v>671.7905566952834</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>277.5</v>
+        <v>43.3</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>67.27299779714681</v>
+        <v>61.65962029444346</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>42.10564059614153</v>
+        <v>33.07690454384492</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>2.680924979238654</v>
+        <v>0.6355856091313873</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>3.574014485894081</v>
+        <v>0.2011002419526808</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6716</v>
+        <v>6642</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>579.3701600037708</v>
+        <v>643.876266043383</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>101.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>55.4152093710048</v>
+        <v>57.72780662450793</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>30.517925978632</v>
+        <v>48.62108380294135</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.645106243703491</v>
+        <v>0.5472873004431631</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>1</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.1301874647917549</v>
+        <v>-0.3804096659107756</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6560</v>
+        <v>6667</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>576.1836478335406</v>
+        <v>643.5725235161178</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>39.4</v>
+        <v>276</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>57.1666773675488</v>
+        <v>52.98499195340806</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>16.60528586385063</v>
+        <v>13.00257694839311</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.53148379608351</v>
+        <v>1.017583160482985</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.0861768384805142</v>
+        <v>0.9738167505442284</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6790</v>
+        <v>6556</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>永豐實</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>571.142565530557</v>
+        <v>642.3039302909681</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>40.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>59.88878985672546</v>
+        <v>50.27271562211735</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>18.00321076005402</v>
+        <v>44.29963857553837</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.048669634508616</v>
+        <v>0.7734876764823726</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.07740803828901389</v>
+        <v>-0.0829972078972319</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6683</v>
+        <v>6821</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>556.0830680652075</v>
+        <v>633.7862736453555</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>1765</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,49 +2937,49 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>54.20433933151472</v>
+        <v>51.79966699901918</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15.04461327259236</v>
+        <v>23.79300653270465</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.894860299546424</v>
+        <v>1.051845918548445</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>24.13896668637481</v>
+        <v>-0.5784855380015834</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6526</v>
+        <v>6658</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>551.9973076529033</v>
+        <v>605.5457366494919</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>697</v>
+        <v>187.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>56.88915556701539</v>
+        <v>52.52891705430964</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>16.37347354516513</v>
+        <v>29.2602992436781</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.922089992417558</v>
+        <v>0.6501770600095974</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>2.137855023648997</v>
+        <v>-3.19302162926916</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6789</v>
+        <v>6645</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>549.8697855879263</v>
+        <v>586.7688228309562</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>552</v>
+        <v>16.15</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>58.54217400041171</v>
+        <v>67.99008773532259</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>18.45383459328753</v>
+        <v>44.36173380717288</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.346800906590445</v>
+        <v>1.002459256436583</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>5.324064677162529</v>
+        <v>0.3936273441466802</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6695</v>
+        <v>6625</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>534.3531504726326</v>
+        <v>584.1944862921598</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>62.7</v>
+        <v>78.2</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>62.94264900834557</v>
+        <v>62.74671791454562</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>26.96397984444638</v>
+        <v>30.6624466010241</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2.544020292853898</v>
+        <v>1.053803576033235</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.7647128750958876</v>
+        <v>0.476209883404654</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6498</v>
+        <v>6761</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>533.9156511265999</v>
+        <v>584.1218764804454</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>101.5</v>
+        <v>208</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>49.34003112765319</v>
+        <v>52.08284422524215</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>30.83749289894177</v>
+        <v>20.36204159408497</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.823247056972381</v>
+        <v>0.9620087197275879</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,51 +3167,51 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.0202285085577402</v>
+        <v>-0.1506211861551958</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6806</v>
+        <v>6552</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>533.7768356926886</v>
+        <v>579.4535255095825</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>3.51</v>
+        <v>31.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G52" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>31.69502801993506</v>
+        <v>51.81650014808022</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>32.59319589058759</v>
+        <v>16.55366373545049</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.7883069892377202</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.4112821522523093</v>
+        <v>-0.052993610080098</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6512</v>
+        <v>6505</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>513.9074035212645</v>
+        <v>575.9955998124266</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>19.9</v>
+        <v>52.1</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,49 +3255,49 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.27566011458969</v>
+        <v>47.1260716673597</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>8.542249744725112</v>
+        <v>12.25741739513799</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.7279950644402411</v>
+        <v>0.7301750051190599</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M53" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.09639995782188961</v>
+        <v>0.024969354565603</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6690</v>
+        <v>6790</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>永豐實</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>512.3325735756915</v>
+        <v>571.142565530557</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>176</v>
+        <v>40.2</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>50.92302580008206</v>
+        <v>59.88878992699657</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>19.50358614018689</v>
+        <v>18.00321082818643</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7335379913296751</v>
+        <v>1.048669634508616</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.306206631356015</v>
+        <v>0.0774080382168949</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6645</v>
+        <v>6579</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>511.7688228309563</v>
+        <v>569.2522633745973</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>16.15</v>
+        <v>158.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>67.99008766345497</v>
+        <v>50.04183344483413</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>44.36173380717288</v>
+        <v>32.2339416017245</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.002459256436583</v>
+        <v>0.6992483839545097</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.3936273441466802</v>
+        <v>-1.562218972146403</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6515</v>
+        <v>6830</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>489.3169471659968</v>
+        <v>565.2364554355919</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>9450</v>
+        <v>560</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>53.27305543711826</v>
+        <v>43.66386387280037</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>19.219487316882</v>
+        <v>20.09200366029241</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.7195926461025355</v>
+        <v>0.4142260671766856</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>100.8375386824715</v>
+        <v>2.157507181530988</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6788</v>
+        <v>6498</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>486.160235949428</v>
+        <v>533.9156511266</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>429</v>
+        <v>101.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>50.07775390477629</v>
+        <v>49.34003133053091</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>8.605030981592115</v>
+        <v>30.83749318657149</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.7219672441801553</v>
+        <v>0.823247056972381</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.8301672382013354</v>
+        <v>-0.0202285100619594</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6811</v>
+        <v>6735</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>481.7654457124116</v>
+        <v>524.7927878329566</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>226.5</v>
+        <v>96.3</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>52.65433822063392</v>
+        <v>46.22414020652956</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>23.20142146404818</v>
+        <v>15.53233351852111</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.6980257596181096</v>
+        <v>1.739658773428812</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-1.561365105299895</v>
+        <v>-0.3182787387270895</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6589</v>
+        <v>6512</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>480.0267141209765</v>
+        <v>513.9074035212645</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>46.55</v>
+        <v>19.9</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>57.66377946151344</v>
+        <v>52.27566011641599</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>16.71289527409576</v>
+        <v>8.54224973486798</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.8238017555131252</v>
+        <v>0.7279950644402411</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,48 +3591,48 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.4527816990265662</v>
+        <v>0.0963999578321915</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, above_ema60, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6799</v>
+        <v>6806</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>475.187181907466</v>
+        <v>513.7768356926886</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>105</v>
+        <v>3.51</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G60" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>60.24402904935134</v>
+        <v>31.69502811541827</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>28.29930597748505</v>
+        <v>32.59319604937431</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.213343872558099</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.9649656175929648</v>
+        <v>0.4112821524971086</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6761</v>
+        <v>6690</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>469.1218764804453</v>
+        <v>512.3325735756916</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>52.08284420269613</v>
+        <v>50.92302598740255</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>20.36204161327329</v>
+        <v>19.50358625157699</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.9620087197275879</v>
+        <v>0.7335379913296751</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.1506211859079349</v>
+        <v>-0.3062066325923553</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6584</v>
+        <v>6674</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>467.6954132241716</v>
+        <v>512.057025558802</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>649</v>
+        <v>17.65</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>50.696732281589</v>
+        <v>48.77842212668608</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>11.5539485622003</v>
+        <v>16.26510783055443</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.8128651732118849</v>
+        <v>0.5255652938808986</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>1.26055438362922</v>
+        <v>0.008803295129239301</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6570</v>
+        <v>6727</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>453.3647618544869</v>
+        <v>510.3024185380683</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>52.8</v>
+        <v>450</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>47.34911446207632</v>
+        <v>47.76255400350212</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>23.01454747744091</v>
+        <v>19.47046819356156</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3571376021517717</v>
+        <v>0.928160083335957</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,11 +3803,11 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-1.128041155484758</v>
+        <v>-4.211387344886143</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>448.6236662758997</v>
+        <v>498.6236662758997</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>32.2</v>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>61.97429973503314</v>
+        <v>61.97429967657907</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>24.44735790242196</v>
+        <v>24.44735791288744</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>1.40262155747115</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0837460241728718</v>
+        <v>0.0837460242759001</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3866,21 +3866,21 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6754</v>
+        <v>6788</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>448.549726880167</v>
+        <v>486.160235949428</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>45.5</v>
+        <v>429</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>54.14743575246718</v>
+        <v>50.07775392631579</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>22.78925612931175</v>
+        <v>8.605031001344958</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.3542125361842818</v>
+        <v>0.7219672441801553</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.07088204448075321</v>
+        <v>0.8301672377892544</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6792</v>
+        <v>6811</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>448.3306649058077</v>
+        <v>481.7654457124116</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>226.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>51.04780940948508</v>
+        <v>52.65433840154471</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>33.5071617046022</v>
+        <v>23.20142150999087</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5509547201611411</v>
+        <v>0.6980257596181096</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.484675660075913</v>
+        <v>-1.561365106536243</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6781</v>
+        <v>6754</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>430.1887927761334</v>
+        <v>478.549726880167</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>1170</v>
+        <v>45.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>51.08048007738114</v>
+        <v>54.14743598972595</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>13.29284389000629</v>
+        <v>22.78925612076848</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7446386615450644</v>
+        <v>0.3542125361842818</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>3.217338773582202</v>
+        <v>0.0708820442334834</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6505</v>
+        <v>6584</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>425.9955998124266</v>
+        <v>467.6954132241716</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>52.1</v>
+        <v>649</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>47.12607159298363</v>
+        <v>50.69673230606963</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>12.257417395138</v>
+        <v>11.55394857990162</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7301750051190599</v>
+        <v>0.8128651732118849</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0249693546686322</v>
+        <v>1.260554382186791</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6532</v>
+        <v>6743</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>414.1896786838012</v>
+        <v>458.2923284645571</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>90.5</v>
+        <v>29.8</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45.23898353251515</v>
+        <v>57.82062166746006</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>21.11869486785161</v>
+        <v>18.0432037331241</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.479705745896903</v>
+        <v>1.161423604992423</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.4581960048353808</v>
+        <v>-0.1312623415943151</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6735</v>
+        <v>6570</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>409.7927878329567</v>
+        <v>453.3647618544869</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>96.3</v>
+        <v>52.8</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>46.22414017748545</v>
+        <v>47.34911449041203</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>15.53233351870306</v>
+        <v>23.01454755332292</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.739658773428812</v>
+        <v>0.3571376021517717</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.3182787385004317</v>
+        <v>-1.128041155587789</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6782</v>
+        <v>6515</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>409.1934737701745</v>
+        <v>449.3169471659963</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>194</v>
+        <v>9450</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,49 +4209,49 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>47.47805830553362</v>
+        <v>53.27305544512108</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>9.000659979126738</v>
+        <v>19.21948735073976</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.5066555757747726</v>
+        <v>0.7195926461025355</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.4798963422853783</v>
+        <v>100.8375386787621</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6743</v>
+        <v>6589</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>408.2923284645571</v>
+        <v>440.0267141209765</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>29.8</v>
+        <v>46.55</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>57.82062146009446</v>
+        <v>57.66377942830302</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>18.04320367993164</v>
+        <v>16.71289531392918</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.161423604992423</v>
+        <v>0.8238017555131252</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.1312623414088591</v>
+        <v>0.4527816991089884</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6605</v>
+        <v>6533</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>381.5622750314933</v>
+        <v>432.7311794030228</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>137.5</v>
+        <v>206.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,49 +4315,49 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>46.89431997801759</v>
+        <v>44.95832684768683</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>19.11747341544075</v>
+        <v>15.21843485322642</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.7132894935891873</v>
+        <v>0.6918204381998573</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M73" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.9322214891618814</v>
+        <v>-0.6648548496174103</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6674</v>
+        <v>6581</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>372.057025558802</v>
+        <v>425.0902751235434</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>17.65</v>
+        <v>108.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>48.77842181803477</v>
+        <v>49.76498655155802</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16.2651076688339</v>
+        <v>11.65165302870997</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5255652938808986</v>
+        <v>0.4690529937648545</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0088032950571196</v>
+        <v>-0.0618705438310623</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6720</v>
+        <v>6532</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>367.4210052918501</v>
+        <v>414.1896786838012</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>140.5</v>
+        <v>90.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>29.39739551781012</v>
+        <v>45.23898357996033</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>31.33580214817543</v>
+        <v>21.11869491552085</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.450303342079935</v>
+        <v>0.479705745896903</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.4727358499463463</v>
+        <v>-0.4581960048147651</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6597</v>
+        <v>6792</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>360.814712239343</v>
+        <v>408.3306649058077</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>68.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>48.32964858066115</v>
+        <v>51.04780943043348</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>10.42347609098247</v>
+        <v>33.50716169717739</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3939088207467544</v>
+        <v>0.5509547201611411</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.5832922002949049</v>
+        <v>-0.4846756602407596</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6692</v>
+        <v>6823</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>360.7071153476509</v>
+        <v>384.1760586199795</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>26.05</v>
+        <v>71.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>41.7623731986854</v>
+        <v>47.58390495477158</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>20.52385038379314</v>
+        <v>21.79493930782204</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.2544101285892097</v>
+        <v>0.5863697636597439</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.2635562087937022</v>
+        <v>0.6247881820618337</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6643</v>
+        <v>6605</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>358.2912153620135</v>
+        <v>381.5622750314932</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>490.5</v>
+        <v>137.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>40.46496816432481</v>
+        <v>46.89432007220239</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>24.51971017979652</v>
+        <v>19.11747347680149</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.6185567010309279</v>
+        <v>0.7132894935891873</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-2.142068282766999</v>
+        <v>-0.9322214893679396</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6840</v>
+        <v>6781</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>355.048826618995</v>
+        <v>380.1887927761335</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>65.3</v>
+        <v>1170</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>47.5634470519303</v>
+        <v>51.08048014613584</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>18.39760304189986</v>
+        <v>13.29284385751866</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.6025354886735733</v>
+        <v>0.7446386615450644</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.1162131780805</v>
+        <v>3.217338772758016</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6763</v>
+        <v>6782</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>352.5534054969777</v>
+        <v>369.1934737701745</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>46.25</v>
+        <v>194</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>46.2509761111889</v>
+        <v>47.47805835483575</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>21.29150836714168</v>
+        <v>9.000659999307084</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.448466481173205</v>
+        <v>0.5066555757747726</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0164592438719788</v>
+        <v>0.4798963421823758</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6588</v>
+        <v>6657</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>342.3827781314351</v>
+        <v>368.4625727547839</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>101.5</v>
+        <v>35.25</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>37.65698334336755</v>
+        <v>38.8679010852649</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>15.04918030851508</v>
+        <v>21.34565956184991</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.4822172387091584</v>
+        <v>0.3815174826411991</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.4279082224165274</v>
+        <v>0.07092685577059531</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6727</v>
+        <v>6706</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>340.3024185380683</v>
+        <v>368.3875416923727</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>450</v>
+        <v>163.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>47.7625540037006</v>
+        <v>44.27153276060201</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>19.47046816771583</v>
+        <v>16.52511167076671</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.928160083335957</v>
+        <v>0.3659011444030279</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-4.211387344948005</v>
+        <v>-3.179363204128989</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6624</v>
+        <v>6720</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>335.632663035696</v>
+        <v>367.4210052918501</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>40.5</v>
+        <v>140.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>49.99980586007958</v>
+        <v>29.39739587110892</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>11.58394237143308</v>
+        <v>31.33580215160929</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.2552830348807604</v>
+        <v>0.450303342079935</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.192357986611444</v>
+        <v>-0.472735849843318</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6581</v>
+        <v>6597</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>335.0902751235434</v>
+        <v>360.814712239343</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>108.5</v>
+        <v>68.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>49.76498655155802</v>
+        <v>48.32964850120403</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>11.65165309919253</v>
+        <v>10.42347609923444</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4690529937648545</v>
+        <v>0.3939088207467544</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0618705440371158</v>
+        <v>-0.5832922005009753</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6829</v>
+        <v>6692</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>332.459324900383</v>
+        <v>360.7071153476509</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>206</v>
+        <v>26.05</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>49.81814827472579</v>
+        <v>41.76237338870885</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>13.4815597635871</v>
+        <v>20.52385051563295</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.7605121262959292</v>
+        <v>0.2544101285892097</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.3423092771450544</v>
+        <v>0.2635562088967327</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6664</v>
+        <v>6643</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>331.7614307070332</v>
+        <v>358.2912153620135</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>376.5</v>
+        <v>490.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>41.55123328855312</v>
+        <v>40.46496825604412</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>24.29323914853275</v>
+        <v>24.51971017979652</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5927642468895933</v>
+        <v>0.6185567010309279</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,11 +5022,11 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-1.288412153536496</v>
+        <v>-2.142068284621473</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>326.4483545249472</v>
+        <v>356.4483545249473</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>30.65</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>46.10348809036936</v>
+        <v>46.10348850075157</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>22.20720727947837</v>
+        <v>22.20720731955953</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>0.4222916212073135</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.2426863402408002</v>
+        <v>-0.2426863402820115</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6706</v>
+        <v>6840</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>323.3875416923727</v>
+        <v>355.048826618995</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>163.5</v>
+        <v>65.3</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>44.27153274820331</v>
+        <v>47.5634470519303</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>16.52511165813995</v>
+        <v>18.39760298151041</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.3659011444030279</v>
+        <v>0.6025354886735733</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,11 +5128,11 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-3.179363203922929</v>
+        <v>-0.1162131780805</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>319.8774431787958</v>
+        <v>354.8774431787958</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>23.45</v>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>39.7301773951702</v>
+        <v>39.73017716771801</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>22.07372473801992</v>
+        <v>22.0737245394235</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.6512940626343851</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.1767369246799114</v>
+        <v>-0.1767369245253671</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6655</v>
+        <v>6763</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>310.4495637720889</v>
+        <v>352.5534054969779</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>124.5</v>
+        <v>46.25</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>51.28340313794268</v>
+        <v>46.25097618798625</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>15.8100478795475</v>
+        <v>21.29150843321769</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5657729939448729</v>
+        <v>0.448466481173205</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-4.324122121057869</v>
+        <v>-0.0164592440574289</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6568</v>
+        <v>6588</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>307.6277603591737</v>
+        <v>342.3827781314351</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>178</v>
+        <v>101.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>38.03020977373409</v>
+        <v>37.65698335177586</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>27.09176983268223</v>
+        <v>15.04918029302101</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6525787453707013</v>
+        <v>0.4822172387091584</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.9250499367523854</v>
+        <v>0.4279082223031967</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6606</v>
+        <v>6624</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>306.224528019532</v>
+        <v>335.632663035696</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>24.8</v>
+        <v>40.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>38.19134245070239</v>
+        <v>49.99980585946304</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>19.50630581715591</v>
+        <v>11.58394233592898</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4425016761876231</v>
+        <v>0.2552830348807604</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.2178847040855474</v>
+        <v>0.192357986683568</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6753</v>
+        <v>6829</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>305.2350979087792</v>
+        <v>332.459324900383</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>126</v>
+        <v>206</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>51.72140633487151</v>
+        <v>49.81814830268978</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>15.95176594522166</v>
+        <v>13.48155970364886</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.9360228261633722</v>
+        <v>0.7605121262959292</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.8762239699251571</v>
+        <v>-0.3423092771450544</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6552</v>
+        <v>6664</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>299.4535255095825</v>
+        <v>331.7614307070332</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>31.7</v>
+        <v>376.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>51.81650009738009</v>
+        <v>41.55123330681672</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16.55366371462567</v>
+        <v>24.29323912941476</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.7883069892377202</v>
+        <v>0.5927642468895933</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0529936100079789</v>
+        <v>-1.288412154360694</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6669</v>
+        <v>6805</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>298.5491962113559</v>
+        <v>322.7405124707404</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>4675</v>
+        <v>1765</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,49 +5481,49 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>40.56850987954667</v>
+        <v>45.57392621879418</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>17.62238578115655</v>
+        <v>13.42924344623533</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.9946453965494952</v>
+        <v>0.3389280181466114</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M95" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-81.53031674036296</v>
+        <v>-12.76011275610786</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6640</v>
+        <v>6568</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>295.4182381974705</v>
+        <v>307.6277603591737</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>1050</v>
+        <v>178</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>35.27265091107098</v>
+        <v>38.03020979675471</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>25.54312221998825</v>
+        <v>27.09176982529295</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6021964978312506</v>
+        <v>0.6525787453707013</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-2.835834509976096</v>
+        <v>-0.9250499372881222</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5562,21 +5562,21 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6550</v>
+        <v>6640</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>295.3611755891507</v>
+        <v>295.4182381974705</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>13.1</v>
+        <v>1050</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>34.36120641467426</v>
+        <v>35.27265092238763</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>33.24673676720325</v>
+        <v>25.54312215552475</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.4189732423422942</v>
+        <v>0.6021964978312506</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.17968733937248</v>
+        <v>-2.835834511727612</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6796</v>
+        <v>6550</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>290.8477767696615</v>
+        <v>295.3611755891507</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>59.2</v>
+        <v>13.1</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>40.64838192202874</v>
+        <v>34.36120659388189</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>30.24179225089697</v>
+        <v>33.24673675125607</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.6540320107004037</v>
+        <v>0.4189732423422942</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.2795270578133353</v>
+        <v>0.1796873391046045</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6776</v>
+        <v>6796</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>288.6877651489952</v>
+        <v>290.8477767696615</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>58.3</v>
+        <v>59.2</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>44.37358154208055</v>
+        <v>40.64838190270842</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>8.468328757073724</v>
+        <v>30.24179228074077</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.9155324334769604</v>
+        <v>0.6540320107004037</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,11 +5711,11 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.2032686917470088</v>
+        <v>0.2795270578751498</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>286.0355848384412</v>
+        <v>286.0355848384413</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>94.40000000000001</v>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>40.69352523048472</v>
+        <v>40.69352526172378</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>15.51612751417769</v>
+        <v>15.51612760934037</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.5871011708623718</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.8545339806301433</v>
+        <v>-0.8545339811659005</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>272.8551368156045</v>
+        <v>272.8551368156065</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>1120</v>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>41.71665527321606</v>
+        <v>41.7166553073433</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>11.78801913958071</v>
+        <v>11.7880190927739</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.9310115195692188</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-1.89875788314724</v>
+        <v>-1.898757883662178</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6680</v>
+        <v>6655</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>251.256199657423</v>
+        <v>270.4495637720889</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>51</v>
+        <v>124.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>50.76408916857723</v>
+        <v>51.28340313932756</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>6.258219803601015</v>
+        <v>15.81004767918724</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6778188557583713</v>
+        <v>0.5657729939448729</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>1.068765052664456</v>
+        <v>-4.324122121057869</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6805</v>
+        <v>6606</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>247.7405124707403</v>
+        <v>266.224528019532</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>1765</v>
+        <v>24.8</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>45.5739261953299</v>
+        <v>38.19134254905887</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>13.42924343661604</v>
+        <v>19.50630620942653</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.3389280181466114</v>
+        <v>0.4425016761876231</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-12.76011275476864</v>
+        <v>-0.2178847041679712</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6533</v>
+        <v>6753</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>247.7311794030228</v>
+        <v>265.2350979087793</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>206.5</v>
+        <v>126</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>44.95832667700358</v>
+        <v>51.7214064238873</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>15.21843485088124</v>
+        <v>15.95176594081149</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.6918204381998573</v>
+        <v>0.9360228261633722</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.6648548470416893</v>
+        <v>0.8762239695748617</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6546</v>
+        <v>6669</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>244.4288855237263</v>
+        <v>258.5491962113559</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>73</v>
+        <v>4675</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>46.15108576132614</v>
+        <v>40.56850994802908</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>18.0357064548007</v>
+        <v>17.62238577670711</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.5332985941999882</v>
+        <v>0.9946453965494952</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.6569805428944389</v>
+        <v>-81.53031674448444</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6708</v>
+        <v>6680</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>239.6786264150476</v>
+        <v>251.256199657423</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>40.35</v>
+        <v>51</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>51.44937836598459</v>
+        <v>50.76408917818039</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>15.59695582624029</v>
+        <v>6.2582196031085</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.163242318265779</v>
+        <v>0.6778188557583713</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.08707867019558491</v>
+        <v>1.068765052726277</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6614</v>
+        <v>6776</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>237.7454071646601</v>
+        <v>248.6877651489952</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>39.95</v>
+        <v>58.3</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>47.43953314908718</v>
+        <v>44.37358156997974</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>16.71944754232941</v>
+        <v>8.4683288821392</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.6453052123214023</v>
+        <v>0.9155324334769604</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0939069080632929</v>
+        <v>-0.2032686916439828</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6657</v>
+        <v>6546</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>228.4625727547838</v>
+        <v>244.4288855237263</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>35.25</v>
+        <v>73</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>38.86790105467234</v>
+        <v>46.15108583018352</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>21.34565955607683</v>
+        <v>18.03570652668487</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3815174826411991</v>
+        <v>0.5332985941999882</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.07092685591483371</v>
+        <v>-0.6569805431004879</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6803</v>
+        <v>6708</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>224.8035636387671</v>
+        <v>239.6786264150476</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>286.5</v>
+        <v>40.35</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>46.54342861910424</v>
+        <v>51.44937849482854</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>27.63790733276278</v>
+        <v>15.59695582624029</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.051533422168872</v>
+        <v>1.163242318265779</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0469837309550351</v>
+        <v>0.08707867004103929</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6741</v>
+        <v>6803</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>223.8055452800678</v>
+        <v>224.8035636387671</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>62.5</v>
+        <v>286.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>49.0633642395345</v>
+        <v>46.54342856979216</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>12.11721444622808</v>
+        <v>27.63790755437534</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.6104778678352338</v>
+        <v>1.051533422168872</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0465543546934178</v>
+        <v>0.0469837310580806</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6641</v>
+        <v>6741</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>223.3265757096869</v>
+        <v>223.8055452800678</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>18.25</v>
+        <v>62.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>46.35633347477594</v>
+        <v>49.0633642881354</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.37576406130656</v>
+        <v>12.11721446362695</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.9310558360686974</v>
+        <v>0.6104778678352338</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.006079677579913</v>
+        <v>0.0465543546316041</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6823</v>
+        <v>6838</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>214.1760586199795</v>
+        <v>205.2813044570067</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>71.5</v>
+        <v>23.75</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>47.58390493363315</v>
+        <v>28.47352920375702</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>21.79493928925094</v>
+        <v>11.01343550316522</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5863697636597439</v>
+        <v>1.747602752352001</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,11 +6400,11 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.624788182133956</v>
+        <v>-0.029812609240193</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>47.05841450139026</v>
+        <v>47.05841512849518</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>12.19585494341458</v>
+        <v>12.19585492731056</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.6559394536649055</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6504</v>
+        <v>6614</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>201.7457995332745</v>
+        <v>197.7454071646601</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>36.2</v>
+        <v>39.95</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>38.80479957600008</v>
+        <v>47.43953204749739</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>18.92288383452225</v>
+        <v>16.71944837651389</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.7010994702210522</v>
+        <v>0.6453052123214023</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1286387203422696</v>
+        <v>0.0939069095675147</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6722</v>
+        <v>6671</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>194.8857323438012</v>
+        <v>197.6248414597484</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>36</v>
+        <v>24.85</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>33.62272439275695</v>
+        <v>25.44708543706569</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>16.84062838096528</v>
+        <v>19.91169667088106</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.512206191188626</v>
+        <v>0.7896870420858106</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.2397840275484658</v>
+        <v>-0.0237872695953242</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6794</v>
+        <v>6591</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>189.5582387948581</v>
+        <v>197.3813122301618</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>79.2</v>
+        <v>54.2</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>42.96876276109524</v>
+        <v>43.00389954875683</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>13.23992394205302</v>
+        <v>20.72894856800844</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.268353231650395</v>
+        <v>0.4964231679690581</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.2144435726704208</v>
+        <v>-0.1563051597274682</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6534</v>
+        <v>6722</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>186.1979338988448</v>
+        <v>194.8857323438012</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>92.2</v>
+        <v>36</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>48.90916668350344</v>
+        <v>33.62273362544613</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>15.89544218934994</v>
+        <v>16.84062961942728</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.4433180027969358</v>
+        <v>1.512206191188626</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.282999906328732</v>
+        <v>-0.2397840378101561</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6577</v>
+        <v>6641</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>180.2945941642988</v>
+        <v>183.3265757096869</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>74.8</v>
+        <v>18.25</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>29.57112131601578</v>
+        <v>46.35633371589158</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>16.80555868334465</v>
+        <v>17.37576413540287</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.9294594164298764</v>
+        <v>0.9310558360686974</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.700192098007404</v>
+        <v>0.0060796775077926</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6838</v>
+        <v>6504</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>175.2813044570072</v>
+        <v>181.7457995332745</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>23.75</v>
+        <v>36.2</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>28.47352919858575</v>
+        <v>38.80479971949375</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>11.01343544080896</v>
+        <v>18.92288405652544</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.747602752352001</v>
+        <v>0.7010994702210522</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0298126092195873</v>
+        <v>0.1286387203422696</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6486</v>
+        <v>6577</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>169.1664284062964</v>
+        <v>180.2945941642988</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>42.0054914125061</v>
+        <v>29.57112150149675</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.35074106926763</v>
+        <v>16.80555867889461</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.7947920518028754</v>
+        <v>0.9294594164298764</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0620930755422808</v>
+        <v>-0.7001920983989266</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6834,21 +6834,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6768</v>
+        <v>6807</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>168.4603074468059</v>
+        <v>180.0736901402674</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>87.2</v>
+        <v>33.2</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>46.65168478995075</v>
+        <v>39.84228787251436</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>18.4269063054417</v>
+        <v>24.68835071328532</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.4655437619765462</v>
+        <v>0.1644047315681745</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.8861943485530324</v>
+        <v>0.1522677305806622</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6671</v>
+        <v>6835</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>167.6248414597485</v>
+        <v>170.1618274291722</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>24.85</v>
+        <v>36.5</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>25.44708533211588</v>
+        <v>42.64131161004648</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>19.91169667088106</v>
+        <v>13.41184106467056</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.7896870420858106</v>
+        <v>0.1531000932575735</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0237872695438063</v>
+        <v>-0.07145160819452639</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6591</v>
+        <v>6486</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>167.3813122301616</v>
+        <v>169.1664284062964</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>54.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>43.00389946894926</v>
+        <v>42.00549137433338</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>20.72894852329999</v>
+        <v>15.35074107547443</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.4964231679690581</v>
+        <v>0.7947920518028754</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.1563051597171664</v>
+        <v>0.0620930755834906</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6807</v>
+        <v>6768</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>150.0736901402674</v>
+        <v>168.4603074468059</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>33.2</v>
+        <v>87.2</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>39.84228752635093</v>
+        <v>46.65168470220244</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>24.68835062449214</v>
+        <v>18.42690640066989</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.1644047315681745</v>
+        <v>0.4655437619765462</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.1522677305394516</v>
+        <v>-0.8861943487590942</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6835</v>
+        <v>6534</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>140.1618274291722</v>
+        <v>166.1979338988448</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>36.5</v>
+        <v>92.2</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>42.64131149441899</v>
+        <v>48.9091666094915</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>13.41184102672874</v>
+        <v>15.89544223896827</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.1531000932575735</v>
+        <v>0.4433180027969358</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.0714516080399875</v>
+        <v>0.2829999065347853</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6689</v>
+        <v>6794</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>112.3398099931427</v>
+        <v>149.5582387948583</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>66.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>42.1373318087399</v>
+        <v>42.96876269205388</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>12.22420598322783</v>
+        <v>13.23992391137526</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.4625238471459079</v>
+        <v>1.268353231650395</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,62 +7142,115 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.3121926587585154</v>
+        <v>-0.2144435726292112</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
+        <v>6689</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>伊雲谷</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>112.3398099931424</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>42.13733194513263</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>12.22420599285623</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.4625238471459079</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.312192659335483</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
         <v>6561</v>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>是方</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D127" s="2" t="n">
-        <v>70.3438905375957</v>
-      </c>
-      <c r="E127" s="2" t="n">
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>70.34389053759566</v>
+      </c>
+      <c r="E128" s="2" t="n">
         <v>340</v>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H127" s="2" t="n">
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
         <v>42.36525558406976</v>
       </c>
-      <c r="I127" s="2" t="n">
-        <v>15.1961737300739</v>
-      </c>
-      <c r="J127" s="2" t="n">
+      <c r="I128" s="2" t="n">
+        <v>15.19617383784916</v>
+      </c>
+      <c r="J128" s="2" t="n">
         <v>0.6244748519708987</v>
       </c>
-      <c r="K127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N127" s="2" t="n">
-        <v>-1.664401330034454</v>
-      </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>-1.664401331889066</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
